--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E7C53F-C82C-430D-8EC8-78C76516C9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07EF373-EFD4-4CA0-88C2-D673BF2787DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="280">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1112,7 +1112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1157,12 +1157,6 @@
       <charset val="136"/>
       <scheme val="major"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1185,7 +1179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1207,9 +1201,6 @@
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1499,7 +1490,7 @@
     <col min="2" max="2" width="5.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.09765625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.09765625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.796875" style="1"/>
   </cols>
   <sheetData>
@@ -10580,7 +10571,6 @@
       <c r="D689" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E689" s="2"/>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690" s="4">
@@ -10595,7 +10585,6 @@
       <c r="D690" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E690" s="2"/>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691" s="4">
@@ -10610,7 +10599,6 @@
       <c r="D691" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E691" s="2"/>
     </row>
     <row r="692" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A692" s="4">
@@ -10625,7 +10613,7 @@
       <c r="D692" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E692" s="10"/>
+      <c r="E692" s="6"/>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A693" s="4">
@@ -10640,7 +10628,7 @@
       <c r="D693" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E693" s="10"/>
+      <c r="E693" s="6"/>
     </row>
     <row r="694" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A694" s="4">
@@ -10655,7 +10643,7 @@
       <c r="D694" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E694" s="10"/>
+      <c r="E694" s="6"/>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A695" s="4">
@@ -10670,19 +10658,67 @@
       <c r="D695" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E695" s="10"/>
-    </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E696" s="2"/>
+      <c r="E695" s="6"/>
+    </row>
+    <row r="696" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A696" s="4">
+        <v>46189</v>
+      </c>
+      <c r="B696" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="C696" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D696" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E696" s="6"/>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E697" s="2"/>
-    </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E698" s="2"/>
+      <c r="A697" s="4">
+        <v>46189</v>
+      </c>
+      <c r="B697" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="C697" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D697" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E697" s="6"/>
+    </row>
+    <row r="698" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A698" s="4">
+        <v>46189</v>
+      </c>
+      <c r="B698" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C698" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D698" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E698" s="6"/>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E699" s="2"/>
+      <c r="A699" s="4">
+        <v>46189</v>
+      </c>
+      <c r="B699" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="C699" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D699" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E699" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59ADB796-22B1-4953-A089-B112E80490C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525BA16B-5B62-4217-A92A-02D90DA22153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="282">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1109,6 +1109,10 @@
   </si>
   <si>
     <t>high waves</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delay</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -10751,7 +10755,7 @@
         <v>0.375</v>
       </c>
       <c r="C701" s="1" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
       <c r="D701" s="5" t="s">
         <v>111</v>
@@ -10766,7 +10770,7 @@
         <v>0.5</v>
       </c>
       <c r="C702" s="1" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
       <c r="D702" s="5" t="s">
         <v>109</v>
@@ -10781,7 +10785,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C703" s="1" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
       <c r="D703" s="5" t="s">
         <v>111</v>
@@ -10796,7 +10800,7 @@
         <v>0.75</v>
       </c>
       <c r="C704" s="1" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
       <c r="D704" s="5" t="s">
         <v>110</v>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525BA16B-5B62-4217-A92A-02D90DA22153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB8D93-4145-420F-8BB8-7F0DDE1FC08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="281">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -262,9 +262,6 @@
     <t>WOW</t>
   </si>
   <si>
-    <t>Data Processing</t>
-  </si>
-  <si>
     <t>Start operation</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1112,8 +1109,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Delay</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>Non-Offshore</t>
   </si>
 </sst>
 </file>
@@ -2641,7 +2637,7 @@
         <v>53</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2832,7 +2828,7 @@
         <v>0.375</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>54</v>
@@ -2846,7 +2842,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>55</v>
@@ -2860,7 +2856,7 @@
         <v>0.375</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>54</v>
@@ -2874,7 +2870,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>55</v>
@@ -2888,7 +2884,7 @@
         <v>0.375</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>54</v>
@@ -2902,7 +2898,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>55</v>
@@ -2945,7 +2941,7 @@
         <v>53</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2971,7 +2967,7 @@
         <v>53</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2983,7 +2979,7 @@
         <v>53</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2995,7 +2991,7 @@
         <v>53</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3007,7 +3003,7 @@
         <v>53</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3021,7 +3017,7 @@
         <v>53</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3035,7 +3031,7 @@
         <v>53</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3047,7 +3043,7 @@
         <v>53</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3059,7 +3055,7 @@
         <v>53</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3071,7 +3067,7 @@
         <v>53</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3085,7 +3081,7 @@
         <v>53</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3099,7 +3095,7 @@
         <v>53</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3111,7 +3107,7 @@
         <v>53</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3123,7 +3119,7 @@
         <v>53</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3135,7 +3131,7 @@
         <v>53</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3147,7 +3143,7 @@
         <v>53</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3161,7 +3157,7 @@
         <v>53</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3173,7 +3169,7 @@
         <v>53</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3187,7 +3183,7 @@
         <v>53</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3199,7 +3195,7 @@
         <v>53</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -3213,7 +3209,7 @@
         <v>53</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3225,7 +3221,7 @@
         <v>53</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3265,7 +3261,7 @@
         <v>53</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3291,7 +3287,7 @@
         <v>53</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3303,7 +3299,7 @@
         <v>53</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3315,7 +3311,7 @@
         <v>53</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3329,7 +3325,7 @@
         <v>53</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3343,7 +3339,7 @@
         <v>53</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3355,7 +3351,7 @@
         <v>53</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3369,7 +3365,7 @@
         <v>53</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3383,7 +3379,7 @@
         <v>53</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3395,7 +3391,7 @@
         <v>53</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3409,7 +3405,7 @@
         <v>53</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3421,7 +3417,7 @@
         <v>53</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3435,7 +3431,7 @@
         <v>53</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3447,7 +3443,7 @@
         <v>53</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -3461,7 +3457,7 @@
         <v>53</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3475,7 +3471,7 @@
         <v>53</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3515,7 +3511,7 @@
         <v>53</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -3527,7 +3523,7 @@
         <v>53</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3553,7 +3549,7 @@
         <v>53</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3565,7 +3561,7 @@
         <v>53</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3579,7 +3575,7 @@
         <v>53</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3605,7 +3601,7 @@
         <v>53</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3619,7 +3615,7 @@
         <v>53</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3631,7 +3627,7 @@
         <v>53</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3643,7 +3639,7 @@
         <v>53</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3669,7 +3665,7 @@
         <v>53</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3683,7 +3679,7 @@
         <v>53</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3695,7 +3691,7 @@
         <v>53</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3709,7 +3705,7 @@
         <v>53</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -3723,7 +3719,7 @@
         <v>53</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3777,7 +3773,7 @@
         <v>53</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
@@ -3789,7 +3785,7 @@
         <v>53</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3815,7 +3811,7 @@
         <v>53</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3827,7 +3823,7 @@
         <v>53</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3841,7 +3837,7 @@
         <v>53</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3853,7 +3849,7 @@
         <v>53</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3867,7 +3863,7 @@
         <v>53</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3881,7 +3877,7 @@
         <v>53</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3893,7 +3889,7 @@
         <v>53</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3905,7 +3901,7 @@
         <v>53</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3919,7 +3915,7 @@
         <v>53</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3931,7 +3927,7 @@
         <v>53</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3943,7 +3939,7 @@
         <v>53</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3957,7 +3953,7 @@
         <v>53</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3969,7 +3965,7 @@
         <v>53</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3983,7 +3979,7 @@
         <v>53</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -3997,7 +3993,7 @@
         <v>53</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4022,10 +4018,10 @@
         <v>0.375</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4036,10 +4032,10 @@
         <v>0.5</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4050,10 +4046,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4064,10 +4060,10 @@
         <v>0.75</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4078,10 +4074,10 @@
         <v>0.375</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4092,10 +4088,10 @@
         <v>0.5</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4106,10 +4102,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4120,10 +4116,10 @@
         <v>0.75</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4134,10 +4130,10 @@
         <v>0.2638888888888889</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4148,10 +4144,10 @@
         <v>0.35902777777777778</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4160,10 +4156,10 @@
       </c>
       <c r="B201" s="4"/>
       <c r="C201" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -4172,10 +4168,10 @@
       </c>
       <c r="B202" s="4"/>
       <c r="C202" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4186,7 +4182,7 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>28</v>
@@ -4198,10 +4194,10 @@
       </c>
       <c r="B204" s="4"/>
       <c r="C204" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4210,10 +4206,10 @@
       </c>
       <c r="B205" s="4"/>
       <c r="C205" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4224,10 +4220,10 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4236,10 +4232,10 @@
       </c>
       <c r="B207" s="4"/>
       <c r="C207" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4250,7 +4246,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>28</v>
@@ -4262,10 +4258,10 @@
       </c>
       <c r="B209" s="4"/>
       <c r="C209" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4274,10 +4270,10 @@
       </c>
       <c r="B210" s="4"/>
       <c r="C210" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4288,10 +4284,10 @@
         <v>0.5083333333333333</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4302,7 +4298,7 @@
         <v>0.51875000000000004</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>28</v>
@@ -4314,10 +4310,10 @@
       </c>
       <c r="B213" s="4"/>
       <c r="C213" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4328,10 +4324,10 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4340,10 +4336,10 @@
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4352,10 +4348,10 @@
       </c>
       <c r="B216" s="4"/>
       <c r="C216" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4366,10 +4362,10 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4378,10 +4374,10 @@
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4392,10 +4388,10 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
@@ -4406,10 +4402,10 @@
         <v>0.6791666666666667</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4420,7 +4416,7 @@
         <v>0.6791666666666667</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D221" s="5" t="s">
         <v>21</v>
@@ -4434,10 +4430,10 @@
         <v>0.2638888888888889</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4448,7 +4444,7 @@
         <v>0.3576388888888889</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>46</v>
@@ -4460,10 +4456,10 @@
       </c>
       <c r="B224" s="4"/>
       <c r="C224" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
@@ -4472,10 +4468,10 @@
       </c>
       <c r="B225" s="4"/>
       <c r="C225" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4486,7 +4482,7 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D226" s="5" t="s">
         <v>28</v>
@@ -4498,10 +4494,10 @@
       </c>
       <c r="B227" s="4"/>
       <c r="C227" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D227" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="D227" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4510,10 +4506,10 @@
       </c>
       <c r="B228" s="4"/>
       <c r="C228" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4522,10 +4518,10 @@
       </c>
       <c r="B229" s="4"/>
       <c r="C229" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4534,10 +4530,10 @@
       </c>
       <c r="B230" s="4"/>
       <c r="C230" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4548,10 +4544,10 @@
         <v>0.4375</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4560,10 +4556,10 @@
       </c>
       <c r="B232" s="4"/>
       <c r="C232" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4572,10 +4568,10 @@
       </c>
       <c r="B233" s="4"/>
       <c r="C233" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4586,10 +4582,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4598,10 +4594,10 @@
       </c>
       <c r="B235" s="4"/>
       <c r="C235" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4612,10 +4608,10 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
@@ -4626,10 +4622,10 @@
         <v>0.60763888888888884</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4640,7 +4636,7 @@
         <v>0.60763888888888884</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D238" s="5" t="s">
         <v>21</v>
@@ -4654,10 +4650,10 @@
         <v>0.375</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4668,10 +4664,10 @@
         <v>0.5</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4682,10 +4678,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4696,10 +4692,10 @@
         <v>0.75</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4710,10 +4706,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4724,10 +4720,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4736,10 +4732,10 @@
       </c>
       <c r="B245" s="4"/>
       <c r="C245" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
@@ -4748,10 +4744,10 @@
       </c>
       <c r="B246" s="4"/>
       <c r="C246" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
@@ -4762,7 +4758,7 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D247" s="5" t="s">
         <v>28</v>
@@ -4774,10 +4770,10 @@
       </c>
       <c r="B248" s="4"/>
       <c r="C248" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4786,10 +4782,10 @@
       </c>
       <c r="B249" s="4"/>
       <c r="C249" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4798,10 +4794,10 @@
       </c>
       <c r="B250" s="4"/>
       <c r="C250" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
@@ -4810,10 +4806,10 @@
       </c>
       <c r="B251" s="4"/>
       <c r="C251" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4822,10 +4818,10 @@
       </c>
       <c r="B252" s="4"/>
       <c r="C252" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4836,10 +4832,10 @@
         <v>0.44930555555555557</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
@@ -4850,7 +4846,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D254" s="5" t="s">
         <v>28</v>
@@ -4862,10 +4858,10 @@
       </c>
       <c r="B255" s="4"/>
       <c r="C255" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4876,10 +4872,10 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
@@ -4890,7 +4886,7 @@
         <v>0.52430555555555558</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D257" s="5" t="s">
         <v>28</v>
@@ -4902,10 +4898,10 @@
       </c>
       <c r="B258" s="4"/>
       <c r="C258" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4916,10 +4912,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4928,10 +4924,10 @@
       </c>
       <c r="B260" s="4"/>
       <c r="C260" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
@@ -4940,10 +4936,10 @@
       </c>
       <c r="B261" s="4"/>
       <c r="C261" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4954,10 +4950,10 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4966,10 +4962,10 @@
       </c>
       <c r="B263" s="4"/>
       <c r="C263" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4980,10 +4976,10 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
@@ -4994,10 +4990,10 @@
         <v>0.72222222222222221</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5008,7 +5004,7 @@
         <v>0.72222222222222221</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D266" s="5" t="s">
         <v>21</v>
@@ -5022,10 +5018,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5036,10 +5032,10 @@
         <v>0.35486111111111113</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5048,10 +5044,10 @@
       </c>
       <c r="B269" s="4"/>
       <c r="C269" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
@@ -5060,10 +5056,10 @@
       </c>
       <c r="B270" s="4"/>
       <c r="C270" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
@@ -5074,7 +5070,7 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D271" s="5" t="s">
         <v>28</v>
@@ -5086,10 +5082,10 @@
       </c>
       <c r="B272" s="4"/>
       <c r="C272" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5098,10 +5094,10 @@
       </c>
       <c r="B273" s="4"/>
       <c r="C273" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5110,10 +5106,10 @@
       </c>
       <c r="B274" s="4"/>
       <c r="C274" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5122,10 +5118,10 @@
       </c>
       <c r="B275" s="4"/>
       <c r="C275" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5136,10 +5132,10 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
@@ -5148,10 +5144,10 @@
       </c>
       <c r="B277" s="4"/>
       <c r="C277" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5162,10 +5158,10 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
@@ -5174,10 +5170,10 @@
       </c>
       <c r="B279" s="4"/>
       <c r="C279" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5188,10 +5184,10 @@
         <v>0.47222222222222221</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
@@ -5202,10 +5198,10 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5216,7 +5212,7 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D282" s="5" t="s">
         <v>21</v>
@@ -5230,10 +5226,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5244,10 +5240,10 @@
         <v>0.35694444444444445</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5256,10 +5252,10 @@
       </c>
       <c r="B285" s="4"/>
       <c r="C285" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5268,10 +5264,10 @@
       </c>
       <c r="B286" s="4"/>
       <c r="C286" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
@@ -5280,10 +5276,10 @@
       </c>
       <c r="B287" s="4"/>
       <c r="C287" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
@@ -5294,7 +5290,7 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D288" s="5" t="s">
         <v>28</v>
@@ -5306,10 +5302,10 @@
       </c>
       <c r="B289" s="4"/>
       <c r="C289" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5318,10 +5314,10 @@
       </c>
       <c r="B290" s="4"/>
       <c r="C290" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D290" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5332,10 +5328,10 @@
         <v>0.43680555555555556</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
@@ -5344,10 +5340,10 @@
       </c>
       <c r="B292" s="4"/>
       <c r="C292" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
@@ -5358,7 +5354,7 @@
         <v>0.46875</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D293" s="5" t="s">
         <v>28</v>
@@ -5370,10 +5366,10 @@
       </c>
       <c r="B294" s="4"/>
       <c r="C294" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5382,10 +5378,10 @@
       </c>
       <c r="B295" s="4"/>
       <c r="C295" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5396,10 +5392,10 @@
         <v>0.4861111111111111</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
@@ -5410,7 +5406,7 @@
         <v>0.4909722222222222</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D297" s="5" t="s">
         <v>28</v>
@@ -5422,10 +5418,10 @@
       </c>
       <c r="B298" s="4"/>
       <c r="C298" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5436,10 +5432,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
@@ -5450,7 +5446,7 @@
         <v>0.52430555555555558</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D300" s="5" t="s">
         <v>28</v>
@@ -5462,10 +5458,10 @@
       </c>
       <c r="B301" s="4"/>
       <c r="C301" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5476,10 +5472,10 @@
         <v>0.56041666666666667</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
@@ -5488,10 +5484,10 @@
       </c>
       <c r="B303" s="4"/>
       <c r="C303" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5502,10 +5498,10 @@
         <v>0.61111111111111116</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5516,10 +5512,10 @@
         <v>0.61805555555555558</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
@@ -5530,10 +5526,10 @@
         <v>0.70486111111111116</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5544,10 +5540,10 @@
         <v>0.70486111111111116</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5558,10 +5554,10 @@
         <v>0.27152777777777776</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5572,10 +5568,10 @@
         <v>0.35069444444444442</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5584,10 +5580,10 @@
       </c>
       <c r="B310" s="4"/>
       <c r="C310" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
@@ -5598,10 +5594,10 @@
         <v>0.375</v>
       </c>
       <c r="C311" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D311" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="D311" s="7" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5612,10 +5608,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D312" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
@@ -5626,10 +5622,10 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5640,10 +5636,10 @@
         <v>0.52430555555555558</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
@@ -5654,7 +5650,7 @@
         <v>0.53472222222222221</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D315" s="5" t="s">
         <v>28</v>
@@ -5666,10 +5662,10 @@
       </c>
       <c r="B316" s="4"/>
       <c r="C316" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
@@ -5678,10 +5674,10 @@
       </c>
       <c r="B317" s="4"/>
       <c r="C317" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5692,10 +5688,10 @@
         <v>0.43680555555555556</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5704,10 +5700,10 @@
       </c>
       <c r="B319" s="4"/>
       <c r="C319" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5716,10 +5712,10 @@
       </c>
       <c r="B320" s="4"/>
       <c r="C320" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D320" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5730,10 +5726,10 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
@@ -5744,7 +5740,7 @@
         <v>0.57638888888888884</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D322" s="5" t="s">
         <v>28</v>
@@ -5756,10 +5752,10 @@
       </c>
       <c r="B323" s="4"/>
       <c r="C323" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5768,10 +5764,10 @@
       </c>
       <c r="B324" s="4"/>
       <c r="C324" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5782,10 +5778,10 @@
         <v>0.61111111111111116</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
@@ -5794,10 +5790,10 @@
       </c>
       <c r="B326" s="4"/>
       <c r="C326" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5808,10 +5804,10 @@
         <v>0.63194444444444442</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5820,10 +5816,10 @@
       </c>
       <c r="B328" s="4"/>
       <c r="C328" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D328" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5834,10 +5830,10 @@
         <v>0.65277777777777779</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
@@ -5848,10 +5844,10 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5862,10 +5858,10 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5876,10 +5872,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5890,10 +5886,10 @@
         <v>0.33611111111111114</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5902,10 +5898,10 @@
       </c>
       <c r="B334" s="4"/>
       <c r="C334" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
@@ -5916,7 +5912,7 @@
         <v>0.36805555555555558</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D335" s="5" t="s">
         <v>28</v>
@@ -5928,10 +5924,10 @@
       </c>
       <c r="B336" s="4"/>
       <c r="C336" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5940,10 +5936,10 @@
       </c>
       <c r="B337" s="4"/>
       <c r="C337" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5954,10 +5950,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
@@ -5966,10 +5962,10 @@
       </c>
       <c r="B339" s="4"/>
       <c r="C339" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5980,10 +5976,10 @@
         <v>6.25E-2</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
@@ -5992,10 +5988,10 @@
       </c>
       <c r="B341" s="4"/>
       <c r="C341" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6006,10 +6002,10 @@
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D342" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6018,10 +6014,10 @@
       </c>
       <c r="B343" s="4"/>
       <c r="C343" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D343" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6032,10 +6028,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D344" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
@@ -6046,10 +6042,10 @@
         <v>0.76388888888888884</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D345" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6060,10 +6056,10 @@
         <v>0.76388888888888884</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D346" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6074,10 +6070,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D347" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
@@ -6088,10 +6084,10 @@
         <v>0.34236111111111112</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D348" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
@@ -6100,10 +6096,10 @@
       </c>
       <c r="B349" s="4"/>
       <c r="C349" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D349" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6114,10 +6110,10 @@
         <v>0.43055555555555558</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D350" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6128,10 +6124,10 @@
         <v>0.44097222222222221</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D351" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
@@ -6142,10 +6138,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D352" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
@@ -6154,10 +6150,10 @@
       </c>
       <c r="B353" s="4"/>
       <c r="C353" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D353" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6168,10 +6164,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D354" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6182,10 +6178,10 @@
         <v>0.26250000000000001</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D355" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6196,10 +6192,10 @@
         <v>0.34722222222222221</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D356" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6208,10 +6204,10 @@
       </c>
       <c r="B357" s="4"/>
       <c r="C357" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D357" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
@@ -6222,7 +6218,7 @@
         <v>0.36944444444444446</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D358" s="5" t="s">
         <v>28</v>
@@ -6234,10 +6230,10 @@
       </c>
       <c r="B359" s="4"/>
       <c r="C359" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D359" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6246,10 +6242,10 @@
       </c>
       <c r="B360" s="4"/>
       <c r="C360" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D360" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6260,10 +6256,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D361" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.3">
@@ -6274,7 +6270,7 @@
         <v>0.40277777777777779</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D362" s="5" t="s">
         <v>28</v>
@@ -6286,10 +6282,10 @@
       </c>
       <c r="B363" s="4"/>
       <c r="C363" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D363" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6298,10 +6294,10 @@
       </c>
       <c r="B364" s="4"/>
       <c r="C364" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D364" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6312,10 +6308,10 @@
         <v>0.4375</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D365" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
@@ -6324,10 +6320,10 @@
       </c>
       <c r="B366" s="4"/>
       <c r="C366" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D366" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6338,10 +6334,10 @@
         <v>0.5</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
@@ -6350,10 +6346,10 @@
       </c>
       <c r="B368" s="4"/>
       <c r="C368" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="369" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6364,10 +6360,10 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D369" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="370" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6376,10 +6372,10 @@
       </c>
       <c r="B370" s="4"/>
       <c r="C370" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D370" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="371" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6390,10 +6386,10 @@
         <v>0.5625</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D371" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.3">
@@ -6404,10 +6400,10 @@
         <v>0.67013888888888884</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D372" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="373" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6418,10 +6414,10 @@
         <v>0.67013888888888884</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D373" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.3">
@@ -6432,10 +6428,10 @@
         <v>0.375</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D374" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.3">
@@ -6446,10 +6442,10 @@
         <v>0.5</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D375" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.3">
@@ -6460,10 +6456,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D376" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.3">
@@ -6474,10 +6470,10 @@
         <v>0.75</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D377" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="378" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -6488,10 +6484,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D378" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E378" s="8"/>
     </row>
@@ -6503,10 +6499,10 @@
         <v>0.28472222222222221</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D379" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E379" s="8"/>
     </row>
@@ -6516,10 +6512,10 @@
       </c>
       <c r="B380" s="4"/>
       <c r="C380" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D380" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E380" s="8"/>
     </row>
@@ -6531,10 +6527,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D381" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E381" s="8"/>
     </row>
@@ -6544,7 +6540,7 @@
       </c>
       <c r="B382" s="4"/>
       <c r="C382" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D382" s="5" t="s">
         <v>21</v>
@@ -6559,10 +6555,10 @@
         <v>0.25347222222222221</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D383" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.3">
@@ -6573,10 +6569,10 @@
         <v>0.3347222222222222</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D384" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6585,10 +6581,10 @@
       </c>
       <c r="B385" s="4"/>
       <c r="C385" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D385" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.3">
@@ -6599,7 +6595,7 @@
         <v>0.35972222222222222</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D386" s="5" t="s">
         <v>28</v>
@@ -6611,10 +6607,10 @@
       </c>
       <c r="B387" s="4"/>
       <c r="C387" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6625,10 +6621,10 @@
         <v>0.40277777777777779</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D388" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6637,10 +6633,10 @@
       </c>
       <c r="B389" s="4"/>
       <c r="C389" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D389" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
@@ -6649,10 +6645,10 @@
       </c>
       <c r="B390" s="4"/>
       <c r="C390" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D390" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6663,10 +6659,10 @@
         <v>0.44444444444444442</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D391" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6677,10 +6673,10 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D392" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6689,10 +6685,10 @@
       </c>
       <c r="B393" s="4"/>
       <c r="C393" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D393" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
@@ -6701,10 +6697,10 @@
       </c>
       <c r="B394" s="4"/>
       <c r="C394" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D394" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6715,10 +6711,10 @@
         <v>0.5</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D395" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6727,10 +6723,10 @@
       </c>
       <c r="B396" s="4"/>
       <c r="C396" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D396" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6741,10 +6737,10 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
@@ -6753,10 +6749,10 @@
       </c>
       <c r="B398" s="4"/>
       <c r="C398" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D398" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6767,10 +6763,10 @@
         <v>0.61111111111111116</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D399" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
@@ -6781,10 +6777,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D400" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6795,7 +6791,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D401" s="5" t="s">
         <v>21</v>
@@ -6809,10 +6805,10 @@
         <v>0.25833333333333336</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D402" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6823,10 +6819,10 @@
         <v>0.34305555555555556</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D403" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
@@ -6835,10 +6831,10 @@
       </c>
       <c r="B404" s="4"/>
       <c r="C404" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6849,10 +6845,10 @@
         <v>0.35902777777777778</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
@@ -6861,10 +6857,10 @@
       </c>
       <c r="B406" s="4"/>
       <c r="C406" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
@@ -6875,7 +6871,7 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D407" s="5" t="s">
         <v>28</v>
@@ -6887,10 +6883,10 @@
       </c>
       <c r="B408" s="4"/>
       <c r="C408" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
@@ -6899,10 +6895,10 @@
       </c>
       <c r="B409" s="4"/>
       <c r="C409" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
@@ -6913,10 +6909,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
@@ -6927,7 +6923,7 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D411" s="5" t="s">
         <v>28</v>
@@ -6939,10 +6935,10 @@
       </c>
       <c r="B412" s="4"/>
       <c r="C412" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
@@ -6953,10 +6949,10 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
@@ -6967,7 +6963,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D414" s="5" t="s">
         <v>28</v>
@@ -6979,10 +6975,10 @@
       </c>
       <c r="B415" s="4"/>
       <c r="C415" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.3">
@@ -6991,10 +6987,10 @@
       </c>
       <c r="B416" s="4"/>
       <c r="C416" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D416" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
@@ -7003,10 +6999,10 @@
       </c>
       <c r="B417" s="4"/>
       <c r="C417" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D417" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.3">
@@ -7015,10 +7011,10 @@
       </c>
       <c r="B418" s="4"/>
       <c r="C418" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D418" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.3">
@@ -7029,10 +7025,10 @@
         <v>0.48333333333333334</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.3">
@@ -7041,10 +7037,10 @@
       </c>
       <c r="B420" s="4"/>
       <c r="C420" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D420" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="D420" s="5" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.3">
@@ -7055,10 +7051,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.3">
@@ -7067,10 +7063,10 @@
       </c>
       <c r="B422" s="4"/>
       <c r="C422" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.3">
@@ -7081,10 +7077,10 @@
         <v>0.57638888888888884</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.3">
@@ -7093,10 +7089,10 @@
       </c>
       <c r="B424" s="4"/>
       <c r="C424" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="425" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7107,10 +7103,10 @@
         <v>0.59722222222222221</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
@@ -7121,10 +7117,10 @@
         <v>0.70138888888888884</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="427" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7135,7 +7131,7 @@
         <v>0.70138888888888884</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D427" s="5" t="s">
         <v>21</v>
@@ -7149,10 +7145,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7163,10 +7159,10 @@
         <v>0.33680555555555558</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
@@ -7177,10 +7173,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7189,10 +7185,10 @@
       </c>
       <c r="B431" s="4"/>
       <c r="C431" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="432" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7201,10 +7197,10 @@
       </c>
       <c r="B432" s="4"/>
       <c r="C432" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D432" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7213,10 +7209,10 @@
       </c>
       <c r="B433" s="4"/>
       <c r="C433" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D433" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.3">
@@ -7225,10 +7221,10 @@
       </c>
       <c r="B434" s="4"/>
       <c r="C434" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D434" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7239,10 +7235,10 @@
         <v>0.40277777777777779</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D435" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.3">
@@ -7253,7 +7249,7 @@
         <v>0.40972222222222221</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D436" s="5" t="s">
         <v>28</v>
@@ -7265,10 +7261,10 @@
       </c>
       <c r="B437" s="4"/>
       <c r="C437" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D437" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7277,10 +7273,10 @@
       </c>
       <c r="B438" s="4"/>
       <c r="C438" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D438" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7289,10 +7285,10 @@
       </c>
       <c r="B439" s="4"/>
       <c r="C439" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D439" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.3">
@@ -7303,10 +7299,10 @@
         <v>0.46180555555555558</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D440" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7315,10 +7311,10 @@
       </c>
       <c r="B441" s="4"/>
       <c r="C441" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D441" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.3">
@@ -7329,10 +7325,10 @@
         <v>0.51388888888888884</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D442" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7341,10 +7337,10 @@
       </c>
       <c r="B443" s="4"/>
       <c r="C443" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D443" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7355,10 +7351,10 @@
         <v>0.53125</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D444" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.3">
@@ -7367,10 +7363,10 @@
       </c>
       <c r="B445" s="4"/>
       <c r="C445" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D445" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="446" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7381,10 +7377,10 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D446" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.3">
@@ -7395,10 +7391,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D447" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="448" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7409,7 +7405,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D448" s="5" t="s">
         <v>21</v>
@@ -7423,10 +7419,10 @@
         <v>0.25</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D449" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="450" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7437,10 +7433,10 @@
         <v>0.33680555555555558</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D450" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.3">
@@ -7451,10 +7447,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D451" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="452" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7465,10 +7461,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D452" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="453" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7477,10 +7473,10 @@
       </c>
       <c r="B453" s="4"/>
       <c r="C453" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D453" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="454" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7489,10 +7485,10 @@
       </c>
       <c r="B454" s="4"/>
       <c r="C454" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D454" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.3">
@@ -7501,10 +7497,10 @@
       </c>
       <c r="B455" s="4"/>
       <c r="C455" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D455" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.3">
@@ -7515,10 +7511,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D456" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="457" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7527,10 +7523,10 @@
       </c>
       <c r="B457" s="4"/>
       <c r="C457" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D457" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="458" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7539,10 +7535,10 @@
       </c>
       <c r="B458" s="4"/>
       <c r="C458" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D458" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="459" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7553,10 +7549,10 @@
         <v>0.5625</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D459" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="460" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7565,10 +7561,10 @@
       </c>
       <c r="B460" s="4"/>
       <c r="C460" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D460" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="461" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7579,10 +7575,10 @@
         <v>0.69444444444444442</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D461" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.3">
@@ -7591,7 +7587,7 @@
       </c>
       <c r="B462" s="4"/>
       <c r="C462" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D462" s="5" t="s">
         <v>21</v>
@@ -7605,10 +7601,10 @@
         <v>0.25</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D463" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="464" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7619,10 +7615,10 @@
         <v>0.28472222222222221</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D464" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.3">
@@ -7633,10 +7629,10 @@
         <v>0.37152777777777779</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D465" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="466" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7647,10 +7643,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D466" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="467" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7659,10 +7655,10 @@
       </c>
       <c r="B467" s="4"/>
       <c r="C467" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D467" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="468" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7671,10 +7667,10 @@
       </c>
       <c r="B468" s="4"/>
       <c r="C468" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D468" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.3">
@@ -7683,10 +7679,10 @@
       </c>
       <c r="B469" s="4"/>
       <c r="C469" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D469" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.3">
@@ -7697,10 +7693,10 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D470" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="471" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7711,10 +7707,10 @@
         <v>0.4375</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D471" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="472" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7723,10 +7719,10 @@
       </c>
       <c r="B472" s="4"/>
       <c r="C472" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D472" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="473" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7735,10 +7731,10 @@
       </c>
       <c r="B473" s="4"/>
       <c r="C473" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D473" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="474" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7749,10 +7745,10 @@
         <v>0.46875</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D474" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.3">
@@ -7763,10 +7759,10 @@
         <v>0.47222222222222221</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D475" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="476" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7775,10 +7771,10 @@
       </c>
       <c r="B476" s="4"/>
       <c r="C476" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D476" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="477" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7787,10 +7783,10 @@
       </c>
       <c r="B477" s="4"/>
       <c r="C477" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D477" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="478" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7801,10 +7797,10 @@
         <v>0.5</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D478" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.3">
@@ -7815,10 +7811,10 @@
         <v>0.51388888888888884</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D479" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="480" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7827,10 +7823,10 @@
       </c>
       <c r="B480" s="4"/>
       <c r="C480" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D480" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="481" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7841,10 +7837,10 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D481" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="482" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7853,10 +7849,10 @@
       </c>
       <c r="B482" s="4"/>
       <c r="C482" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D482" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.3">
@@ -7865,10 +7861,10 @@
       </c>
       <c r="B483" s="4"/>
       <c r="C483" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D483" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="484" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7879,10 +7875,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D484" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="485" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7891,10 +7887,10 @@
       </c>
       <c r="B485" s="4"/>
       <c r="C485" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D485" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="486" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7903,10 +7899,10 @@
       </c>
       <c r="B486" s="4"/>
       <c r="C486" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D486" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.3">
@@ -7917,10 +7913,10 @@
         <v>0.76736111111111116</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D487" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="488" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7929,7 +7925,7 @@
       </c>
       <c r="B488" s="4"/>
       <c r="C488" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D488" s="5" t="s">
         <v>21</v>
@@ -7943,10 +7939,10 @@
         <v>0.25</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D489" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="490" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7957,10 +7953,10 @@
         <v>0.27777777777777779</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D490" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.3">
@@ -7971,10 +7967,10 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D491" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="492" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7983,10 +7979,10 @@
       </c>
       <c r="B492" s="4"/>
       <c r="C492" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D492" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="493" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7997,10 +7993,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D493" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="494" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8009,10 +8005,10 @@
       </c>
       <c r="B494" s="4"/>
       <c r="C494" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D494" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="495" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8023,10 +8019,10 @@
         <v>0.43055555555555558</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D495" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="496" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8035,10 +8031,10 @@
       </c>
       <c r="B496" s="4"/>
       <c r="C496" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D496" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="497" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8049,10 +8045,10 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D497" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.3">
@@ -8061,10 +8057,10 @@
       </c>
       <c r="B498" s="4"/>
       <c r="C498" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D498" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="499" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8075,10 +8071,10 @@
         <v>0.49513888888888891</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D499" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="500" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8087,10 +8083,10 @@
       </c>
       <c r="B500" s="4"/>
       <c r="C500" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D500" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.3">
@@ -8099,10 +8095,10 @@
       </c>
       <c r="B501" s="4"/>
       <c r="C501" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D501" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="502" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8113,10 +8109,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D502" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="503" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8125,10 +8121,10 @@
       </c>
       <c r="B503" s="4"/>
       <c r="C503" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D503" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="504" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8137,10 +8133,10 @@
       </c>
       <c r="B504" s="4"/>
       <c r="C504" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D504" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.3">
@@ -8151,10 +8147,10 @@
         <v>0.71527777777777779</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D505" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="506" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8163,7 +8159,7 @@
       </c>
       <c r="B506" s="4"/>
       <c r="C506" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D506" s="5" t="s">
         <v>21</v>
@@ -8177,10 +8173,10 @@
         <v>0.25</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D507" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="508" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8191,10 +8187,10 @@
         <v>0.26250000000000001</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D508" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.3">
@@ -8205,10 +8201,10 @@
         <v>0.34722222222222221</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D509" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="510" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8217,10 +8213,10 @@
       </c>
       <c r="B510" s="4"/>
       <c r="C510" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D510" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="511" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8231,10 +8227,10 @@
         <v>0.36805555555555558</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D511" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="512" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8243,10 +8239,10 @@
       </c>
       <c r="B512" s="4"/>
       <c r="C512" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D512" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="513" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8257,10 +8253,10 @@
         <v>0.38680555555555557</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D513" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="514" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8269,10 +8265,10 @@
       </c>
       <c r="B514" s="4"/>
       <c r="C514" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D514" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.3">
@@ -8281,10 +8277,10 @@
       </c>
       <c r="B515" s="4"/>
       <c r="C515" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D515" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="516" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8295,10 +8291,10 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D516" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="517" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8307,10 +8303,10 @@
       </c>
       <c r="B517" s="4"/>
       <c r="C517" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D517" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="518" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8319,10 +8315,10 @@
       </c>
       <c r="B518" s="4"/>
       <c r="C518" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D518" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="519" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8333,10 +8329,10 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D519" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="520" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8345,7 +8341,7 @@
       </c>
       <c r="B520" s="4"/>
       <c r="C520" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D520" s="5" t="s">
         <v>21</v>
@@ -8359,10 +8355,10 @@
         <v>0.25833333333333336</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D521" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="522" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8373,10 +8369,10 @@
         <v>0.34027777777777779</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D522" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.3">
@@ -8385,10 +8381,10 @@
       </c>
       <c r="B523" s="4"/>
       <c r="C523" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D523" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="524" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8397,10 +8393,10 @@
       </c>
       <c r="B524" s="4"/>
       <c r="C524" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D524" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.3">
@@ -8411,10 +8407,10 @@
         <v>0.43055555555555558</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D525" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="526" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8425,10 +8421,10 @@
         <v>0.53125</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D526" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="527" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8437,7 +8433,7 @@
       </c>
       <c r="B527" s="4"/>
       <c r="C527" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D527" s="5" t="s">
         <v>21</v>
@@ -8451,10 +8447,10 @@
         <v>0.375</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D528" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="529" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8465,10 +8461,10 @@
         <v>0.5</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D529" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.3">
@@ -8479,10 +8475,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D530" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="531" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8493,10 +8489,10 @@
         <v>0.75</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D531" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="532" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8507,10 +8503,10 @@
         <v>0.375</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D532" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.3">
@@ -8521,10 +8517,10 @@
         <v>0.5</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D533" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="534" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8535,10 +8531,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D534" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.3">
@@ -8549,10 +8545,10 @@
         <v>0.75</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D535" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="536" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8563,10 +8559,10 @@
         <v>0.375</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D536" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.3">
@@ -8577,10 +8573,10 @@
         <v>0.5</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D537" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="538" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8591,10 +8587,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D538" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.3">
@@ -8605,10 +8601,10 @@
         <v>0.75</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D539" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="540" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8619,10 +8615,10 @@
         <v>0.375</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D540" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.3">
@@ -8633,10 +8629,10 @@
         <v>0.5</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D541" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="542" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8647,10 +8643,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D542" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.3">
@@ -8661,10 +8657,10 @@
         <v>0.75</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D543" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.3">
@@ -8675,10 +8671,10 @@
         <v>0.375</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D544" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.3">
@@ -8689,10 +8685,10 @@
         <v>0.5</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D545" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.3">
@@ -8703,10 +8699,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C546" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D546" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.3">
@@ -8717,10 +8713,10 @@
         <v>0.75</v>
       </c>
       <c r="C547" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D547" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="548" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8731,10 +8727,10 @@
         <v>0.375</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D548" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.3">
@@ -8745,10 +8741,10 @@
         <v>0.5</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D549" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="550" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8759,10 +8755,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D550" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.3">
@@ -8773,10 +8769,10 @@
         <v>0.75</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D551" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="552" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8787,10 +8783,10 @@
         <v>0.25</v>
       </c>
       <c r="C552" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D552" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.3">
@@ -8801,10 +8797,10 @@
         <v>0.3298611111111111</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D553" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="554" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8813,10 +8809,10 @@
       </c>
       <c r="B554" s="4"/>
       <c r="C554" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D554" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.3">
@@ -8827,10 +8823,10 @@
         <v>0.34930555555555554</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D555" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="556" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8839,10 +8835,10 @@
       </c>
       <c r="B556" s="4"/>
       <c r="C556" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D556" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="557" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8853,10 +8849,10 @@
         <v>0.25</v>
       </c>
       <c r="C557" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D557" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.3">
@@ -8867,10 +8863,10 @@
         <v>0.3298611111111111</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D558" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.3">
@@ -8879,10 +8875,10 @@
       </c>
       <c r="B559" s="4"/>
       <c r="C559" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D559" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="560" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8893,10 +8889,10 @@
         <v>0.34930555555555554</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D560" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.3">
@@ -8905,10 +8901,10 @@
       </c>
       <c r="B561" s="4"/>
       <c r="C561" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D561" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.3">
@@ -8919,10 +8915,10 @@
         <v>0.38333333333333336</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D562" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.3">
@@ -8931,10 +8927,10 @@
       </c>
       <c r="B563" s="4"/>
       <c r="C563" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D563" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.3">
@@ -8945,7 +8941,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D564" s="5" t="s">
         <v>28</v>
@@ -8957,10 +8953,10 @@
       </c>
       <c r="B565" s="4"/>
       <c r="C565" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D565" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.3">
@@ -8969,10 +8965,10 @@
       </c>
       <c r="B566" s="4"/>
       <c r="C566" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D566" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.3">
@@ -8981,10 +8977,10 @@
       </c>
       <c r="B567" s="4"/>
       <c r="C567" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D567" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.3">
@@ -8995,10 +8991,10 @@
         <v>0.46111111111111114</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D568" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.3">
@@ -9009,7 +9005,7 @@
         <v>0.46388888888888891</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D569" s="5" t="s">
         <v>28</v>
@@ -9021,10 +9017,10 @@
       </c>
       <c r="B570" s="4"/>
       <c r="C570" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D570" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.3">
@@ -9033,10 +9029,10 @@
       </c>
       <c r="B571" s="4"/>
       <c r="C571" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D571" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.3">
@@ -9045,10 +9041,10 @@
       </c>
       <c r="B572" s="4"/>
       <c r="C572" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D572" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.3">
@@ -9057,10 +9053,10 @@
       </c>
       <c r="B573" s="4"/>
       <c r="C573" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D573" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.3">
@@ -9071,10 +9067,10 @@
         <v>0.51388888888888884</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D574" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.3">
@@ -9083,10 +9079,10 @@
       </c>
       <c r="B575" s="4"/>
       <c r="C575" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D575" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.3">
@@ -9095,10 +9091,10 @@
       </c>
       <c r="B576" s="4"/>
       <c r="C576" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D576" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.3">
@@ -9109,10 +9105,10 @@
         <v>0.5625</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D577" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.3">
@@ -9121,10 +9117,10 @@
       </c>
       <c r="B578" s="4"/>
       <c r="C578" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D578" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="579" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9135,10 +9131,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D579" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.3">
@@ -9147,7 +9143,7 @@
       </c>
       <c r="B580" s="4"/>
       <c r="C580" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D580" s="5" t="s">
         <v>21</v>
@@ -9161,10 +9157,10 @@
         <v>0.25347222222222221</v>
       </c>
       <c r="C581" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D581" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="D581" s="5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="582" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9175,10 +9171,10 @@
         <v>0.3263888888888889</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D582" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.3">
@@ -9187,10 +9183,10 @@
       </c>
       <c r="B583" s="4"/>
       <c r="C583" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D583" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="584" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9201,7 +9197,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D584" s="5" t="s">
         <v>28</v>
@@ -9213,10 +9209,10 @@
       </c>
       <c r="B585" s="4"/>
       <c r="C585" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D585" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="586" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9225,10 +9221,10 @@
       </c>
       <c r="B586" s="4"/>
       <c r="C586" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D586" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="587" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9237,10 +9233,10 @@
       </c>
       <c r="B587" s="4"/>
       <c r="C587" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D587" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
@@ -9249,10 +9245,10 @@
       </c>
       <c r="B588" s="4"/>
       <c r="C588" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D588" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="589" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9261,10 +9257,10 @@
       </c>
       <c r="B589" s="4"/>
       <c r="C589" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D589" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="590" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9273,10 +9269,10 @@
       </c>
       <c r="B590" s="4"/>
       <c r="C590" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D590" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.3">
@@ -9287,10 +9283,10 @@
         <v>0.40277777777777779</v>
       </c>
       <c r="C591" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D591" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="592" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9301,7 +9297,7 @@
         <v>0.40555555555555556</v>
       </c>
       <c r="C592" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D592" s="5" t="s">
         <v>28</v>
@@ -9313,10 +9309,10 @@
       </c>
       <c r="B593" s="4"/>
       <c r="C593" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D593" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.3">
@@ -9325,10 +9321,10 @@
       </c>
       <c r="B594" s="4"/>
       <c r="C594" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D594" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="595" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9337,10 +9333,10 @@
       </c>
       <c r="B595" s="4"/>
       <c r="C595" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D595" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.3">
@@ -9349,10 +9345,10 @@
       </c>
       <c r="B596" s="4"/>
       <c r="C596" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D596" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="597" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9363,10 +9359,10 @@
         <v>0.4861111111111111</v>
       </c>
       <c r="C597" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D597" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="598" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9377,7 +9373,7 @@
         <v>0.49166666666666664</v>
       </c>
       <c r="C598" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D598" s="5" t="s">
         <v>28</v>
@@ -9389,10 +9385,10 @@
       </c>
       <c r="B599" s="4"/>
       <c r="C599" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D599" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="600" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9403,10 +9399,10 @@
         <v>0.5</v>
       </c>
       <c r="C600" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D600" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="601" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9415,10 +9411,10 @@
       </c>
       <c r="B601" s="4"/>
       <c r="C601" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D601" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
@@ -9427,10 +9423,10 @@
       </c>
       <c r="B602" s="4"/>
       <c r="C602" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D602" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
@@ -9441,10 +9437,10 @@
         <v>0.54513888888888884</v>
       </c>
       <c r="C603" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D603" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
@@ -9453,10 +9449,10 @@
       </c>
       <c r="B604" s="4"/>
       <c r="C604" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D604" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="605" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9467,10 +9463,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C605" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D605" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
@@ -9479,7 +9475,7 @@
       </c>
       <c r="B606" s="4"/>
       <c r="C606" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D606" s="5" t="s">
         <v>21</v>
@@ -9493,10 +9489,10 @@
         <v>0.25</v>
       </c>
       <c r="C607" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D607" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="D607" s="5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="608" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9507,10 +9503,10 @@
         <v>0.32291666666666669</v>
       </c>
       <c r="C608" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D608" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
@@ -9519,10 +9515,10 @@
       </c>
       <c r="B609" s="4"/>
       <c r="C609" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D609" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="610" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9533,7 +9529,7 @@
         <v>0.35555555555555557</v>
       </c>
       <c r="C610" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D610" s="5" t="s">
         <v>28</v>
@@ -9545,10 +9541,10 @@
       </c>
       <c r="B611" s="4"/>
       <c r="C611" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D611" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="612" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9559,10 +9555,10 @@
         <v>0.3923611111111111</v>
       </c>
       <c r="C612" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D612" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="613" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9571,10 +9567,10 @@
       </c>
       <c r="B613" s="4"/>
       <c r="C613" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D613" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
@@ -9583,10 +9579,10 @@
       </c>
       <c r="B614" s="4"/>
       <c r="C614" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D614" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="615" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9595,10 +9591,10 @@
       </c>
       <c r="B615" s="4"/>
       <c r="C615" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D615" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="616" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9609,10 +9605,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="C616" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D616" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="617" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9621,10 +9617,10 @@
       </c>
       <c r="B617" s="4"/>
       <c r="C617" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D617" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="618" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9635,10 +9631,10 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="C618" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D618" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
@@ -9647,7 +9643,7 @@
       </c>
       <c r="B619" s="4"/>
       <c r="C619" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D619" s="5" t="s">
         <v>21</v>
@@ -9661,10 +9657,10 @@
         <v>0.25</v>
       </c>
       <c r="C620" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D620" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="621" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9675,10 +9671,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C621" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D621" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
@@ -9687,10 +9683,10 @@
       </c>
       <c r="B622" s="4"/>
       <c r="C622" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D622" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="623" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9701,7 +9697,7 @@
         <v>0.36458333333333331</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D623" s="5" t="s">
         <v>56</v>
@@ -9715,7 +9711,7 @@
         <v>0.45763888888888887</v>
       </c>
       <c r="C624" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D624" s="5" t="s">
         <v>28</v>
@@ -9729,10 +9725,10 @@
         <v>0.46527777777777779</v>
       </c>
       <c r="C625" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D625" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="626" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9741,10 +9737,10 @@
       </c>
       <c r="B626" s="4"/>
       <c r="C626" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D626" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
@@ -9753,10 +9749,10 @@
       </c>
       <c r="B627" s="4"/>
       <c r="C627" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D627" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
@@ -9767,10 +9763,10 @@
         <v>0.5180555555555556</v>
       </c>
       <c r="C628" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D628" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="629" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9779,10 +9775,10 @@
       </c>
       <c r="B629" s="4"/>
       <c r="C629" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D629" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="630" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9793,10 +9789,10 @@
         <v>0.62152777777777779</v>
       </c>
       <c r="C630" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D630" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.3">
@@ -9805,7 +9801,7 @@
       </c>
       <c r="B631" s="4"/>
       <c r="C631" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D631" s="5" t="s">
         <v>21</v>
@@ -9819,10 +9815,10 @@
         <v>0.25</v>
       </c>
       <c r="C632" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D632" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="633" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9833,10 +9829,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C633" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D633" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.3">
@@ -9845,10 +9841,10 @@
       </c>
       <c r="B634" s="4"/>
       <c r="C634" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D634" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="635" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9859,7 +9855,7 @@
         <v>0.35069444444444442</v>
       </c>
       <c r="C635" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D635" s="5" t="s">
         <v>56</v>
@@ -9873,10 +9869,10 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="C636" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D636" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="637" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9885,10 +9881,10 @@
       </c>
       <c r="B637" s="4"/>
       <c r="C637" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D637" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="638" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9899,10 +9895,10 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="C638" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D638" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.3">
@@ -9911,10 +9907,10 @@
       </c>
       <c r="B639" s="4"/>
       <c r="C639" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D639" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="640" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9925,10 +9921,10 @@
         <v>0.60763888888888884</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D640" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.3">
@@ -9937,7 +9933,7 @@
       </c>
       <c r="B641" s="4"/>
       <c r="C641" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D641" s="5" t="s">
         <v>21</v>
@@ -9951,10 +9947,10 @@
         <v>0.25</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D642" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="643" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9965,10 +9961,10 @@
         <v>0.27708333333333335</v>
       </c>
       <c r="C643" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D643" s="5" t="s">
         <v>269</v>
-      </c>
-      <c r="D643" s="5" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.3">
@@ -9979,10 +9975,10 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D644" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="645" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9991,7 +9987,7 @@
       </c>
       <c r="B645" s="4"/>
       <c r="C645" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D645" s="5" t="s">
         <v>21</v>
@@ -10003,10 +9999,10 @@
       </c>
       <c r="B646" s="4"/>
       <c r="C646" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D646" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="647" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10017,7 +10013,7 @@
         <v>0.375</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D647" s="5" t="s">
         <v>56</v>
@@ -10031,7 +10027,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D648" s="5" t="s">
         <v>21</v>
@@ -10045,10 +10041,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D649" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="650" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10059,10 +10055,10 @@
         <v>0.33541666666666664</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D650" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.3">
@@ -10071,10 +10067,10 @@
       </c>
       <c r="B651" s="4"/>
       <c r="C651" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D651" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="652" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10085,10 +10081,10 @@
         <v>0.3576388888888889</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D652" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="653" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10097,10 +10093,10 @@
       </c>
       <c r="B653" s="4"/>
       <c r="C653" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D653" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="654" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10111,10 +10107,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D654" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="655" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10123,10 +10119,10 @@
       </c>
       <c r="B655" s="4"/>
       <c r="C655" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D655" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.3">
@@ -10137,10 +10133,10 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D656" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="657" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10149,10 +10145,10 @@
       </c>
       <c r="B657" s="4"/>
       <c r="C657" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D657" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.3">
@@ -10163,10 +10159,10 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D658" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.3">
@@ -10175,7 +10171,7 @@
       </c>
       <c r="B659" s="4"/>
       <c r="C659" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D659" s="5" t="s">
         <v>21</v>
@@ -10189,10 +10185,10 @@
         <v>0.375</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D660" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="661" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10203,10 +10199,10 @@
         <v>0.5</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D661" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.3">
@@ -10217,10 +10213,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D662" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="663" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10231,10 +10227,10 @@
         <v>0.75</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D663" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="664" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10245,10 +10241,10 @@
         <v>0.375</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D664" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
@@ -10259,10 +10255,10 @@
         <v>0.5</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D665" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="666" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10273,10 +10269,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D666" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.3">
@@ -10287,10 +10283,10 @@
         <v>0.75</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D667" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="668" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10301,10 +10297,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D668" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.3">
@@ -10315,10 +10311,10 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D669" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="670" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10329,10 +10325,10 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D670" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
@@ -10343,10 +10339,10 @@
         <v>0.34027777777777779</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D671" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="672" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10355,7 +10351,7 @@
       </c>
       <c r="B672" s="4"/>
       <c r="C672" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D672" s="5" t="s">
         <v>21</v>
@@ -10369,10 +10365,10 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D673" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="674" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10383,10 +10379,10 @@
         <v>0.33402777777777776</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D674" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.3">
@@ -10395,10 +10391,10 @@
       </c>
       <c r="B675" s="4"/>
       <c r="C675" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D675" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="676" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10409,10 +10405,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D676" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="677" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10421,10 +10417,10 @@
       </c>
       <c r="B677" s="4"/>
       <c r="C677" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D677" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="678" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10435,10 +10431,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D678" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="679" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10447,10 +10443,10 @@
       </c>
       <c r="B679" s="4"/>
       <c r="C679" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D679" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.3">
@@ -10461,10 +10457,10 @@
         <v>0.53819444444444442</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D680" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="681" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10473,10 +10469,10 @@
       </c>
       <c r="B681" s="4"/>
       <c r="C681" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D681" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.3">
@@ -10487,10 +10483,10 @@
         <v>0.61111111111111116</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D682" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.3">
@@ -10501,10 +10497,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D683" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="684" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10513,7 +10509,7 @@
       </c>
       <c r="B684" s="4"/>
       <c r="C684" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D684" s="5" t="s">
         <v>21</v>
@@ -10527,10 +10523,10 @@
         <v>0.375</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D685" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="686" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10541,10 +10537,10 @@
         <v>0.5</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D686" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.3">
@@ -10555,10 +10551,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C687" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D687" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="688" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10569,10 +10565,10 @@
         <v>0.75</v>
       </c>
       <c r="C688" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D688" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.3">
@@ -10583,10 +10579,10 @@
         <v>0.375</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D689" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.3">
@@ -10597,10 +10593,10 @@
         <v>0.5</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D690" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.3">
@@ -10611,10 +10607,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D691" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.3">
@@ -10625,10 +10621,10 @@
         <v>0.75</v>
       </c>
       <c r="C692" s="1" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D692" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.3">
@@ -10639,10 +10635,10 @@
         <v>0.375</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D693" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.3">
@@ -10653,10 +10649,10 @@
         <v>0.5</v>
       </c>
       <c r="C694" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D694" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.3">
@@ -10667,10 +10663,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D695" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.3">
@@ -10681,10 +10677,10 @@
         <v>0.75</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D696" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="697" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10695,10 +10691,10 @@
         <v>0.375</v>
       </c>
       <c r="C697" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D697" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E697" s="5"/>
     </row>
@@ -10710,10 +10706,10 @@
         <v>0.5</v>
       </c>
       <c r="C698" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D698" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E698" s="5"/>
     </row>
@@ -10725,10 +10721,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C699" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D699" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E699" s="5"/>
     </row>
@@ -10740,10 +10736,10 @@
         <v>0.75</v>
       </c>
       <c r="C700" s="1" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="D700" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E700" s="5"/>
     </row>
@@ -10755,10 +10751,10 @@
         <v>0.375</v>
       </c>
       <c r="C701" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D701" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E701" s="5"/>
     </row>
@@ -10770,10 +10766,10 @@
         <v>0.5</v>
       </c>
       <c r="C702" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D702" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E702" s="5"/>
     </row>
@@ -10785,10 +10781,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C703" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D703" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E703" s="5"/>
     </row>
@@ -10800,10 +10796,10 @@
         <v>0.75</v>
       </c>
       <c r="C704" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D704" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E704" s="5"/>
     </row>
